--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -90,7 +90,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-10-01T14:20:19.954Z</t>
+    <t>2026-10-01T19:45:01.428Z</t>
   </si>
   <si>
     <t xml:space="preserve">Hearing Aids and Hearing Test Centres | Amplifon CA </t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -90,7 +90,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-10-01T19:45:01.428Z</t>
+    <t>2026-10-01T20:04:06.443Z</t>
   </si>
   <si>
     <t xml:space="preserve">Hearing Aids and Hearing Test Centres | Amplifon CA </t>
